--- a/political_youtube/JSON Files/ident_1803/large_german_channels/top200_channelcrawler.xlsx
+++ b/political_youtube/JSON Files/ident_1803/large_german_channels/top200_channelcrawler.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\PycharmProjects\youtube_data\political_youtube\JSON Files\ident_1803\large_german_channels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyhcarmProjects\youtube_data\political_youtube\JSON Files\ident_1803\large_german_channels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA12F6B-5827-47BD-9DAA-C0552E8595B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362CE649-9A05-4E56-8300-385274B3BAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="6848" windowHeight="13043" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10632" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
     <t>name</t>
   </si>
@@ -914,6 +927,321 @@
   </si>
   <si>
     <t>UCh24_9600fCJemez4RgoOmw</t>
+  </si>
+  <si>
+    <t>UCb5TfGtSgvNPVPQawfCFuAw</t>
+  </si>
+  <si>
+    <t>UCBzai1GXVKDdVCrwlKZg_6Q</t>
+  </si>
+  <si>
+    <t>UCIk-Fw1QuWJdO4sAxhXE5DA</t>
+  </si>
+  <si>
+    <t>UClCZul-nK9h8eVo7REC7RGA</t>
+  </si>
+  <si>
+    <t>UCYisdU_KhanzKLQlMPe5zGA</t>
+  </si>
+  <si>
+    <t>UCnVTsgPKj7tKrDAC2IsRp9A</t>
+  </si>
+  <si>
+    <t>UCBnqM-sZxMRm2hnVo6wSQ8w</t>
+  </si>
+  <si>
+    <t>UCoKCF-pUbhJtSsSGs6JCLfQ</t>
+  </si>
+  <si>
+    <t>UCCljzsYpepeNeY-nKPBKnhA</t>
+  </si>
+  <si>
+    <t>UCOQFfcGRc886dXP2Oyt5OEg</t>
+  </si>
+  <si>
+    <t>UC4psZiwQ7Iw2ypKcK7k2a-A</t>
+  </si>
+  <si>
+    <t>UCOfQ0nZG7YClwNSaL-xULKQ</t>
+  </si>
+  <si>
+    <t>UCZPAni75bkLnjGO8yhuJpdw</t>
+  </si>
+  <si>
+    <t>UCFn1ROV1cysLXMkS53Aw6PQ</t>
+  </si>
+  <si>
+    <t>UCiiGHI0DtajhSqQtf0478hA</t>
+  </si>
+  <si>
+    <t>UCgrHgV7atBftQk8dXwIDktg</t>
+  </si>
+  <si>
+    <t>UCi7lrRpU8mVZ4QNCPIcadUw</t>
+  </si>
+  <si>
+    <t>UC_d3KXxOJx2WaS4kQ5eJePw</t>
+  </si>
+  <si>
+    <t>UCnytvQ-VexQ43pYx6KX-DPw</t>
+  </si>
+  <si>
+    <t>UCTkYT9IjUuhmkXbwYEohIwQ</t>
+  </si>
+  <si>
+    <t>UC9Iq-yi4q3lsnSEXltzpqcQ</t>
+  </si>
+  <si>
+    <t>UCq880QL0THPePYuGKV7PxZw</t>
+  </si>
+  <si>
+    <t>UCM5gP5bRLmc7ysiLbXA2R3A</t>
+  </si>
+  <si>
+    <t>UCIp8Syqe13rKfkybPq_udWQ</t>
+  </si>
+  <si>
+    <t>UCBYxq7eD0UgOF0lGltd1ItQ</t>
+  </si>
+  <si>
+    <t>UCeRAFi29YbP0de5LtRG2UMw</t>
+  </si>
+  <si>
+    <t>UCD52HZzU0qxNHUCEkPgSJaA</t>
+  </si>
+  <si>
+    <t>UCqLv2nTsMB_FXtQRFNXjWhA</t>
+  </si>
+  <si>
+    <t>UCGMVBv0w5tIGuwGT-Tgu2Lw</t>
+  </si>
+  <si>
+    <t>UCmW4T08z29y3VDAkPOIpIjg</t>
+  </si>
+  <si>
+    <t>UCWZu-P34DVZUVrYAROU3Cmw</t>
+  </si>
+  <si>
+    <t>UCfZhCLT9UmzRl1byZguPoHA</t>
+  </si>
+  <si>
+    <t>UCxQTon4gUs00H48vEeFYmZQ</t>
+  </si>
+  <si>
+    <t>UCa7IcQjnxZTOLgdNU14Hydg</t>
+  </si>
+  <si>
+    <t>UChiFVh8U2d6cyJIh0ghNF3w</t>
+  </si>
+  <si>
+    <t>UCinuZeKpeDJRJ2w8n3PZmzg</t>
+  </si>
+  <si>
+    <t>UCJiRXf1Pb0ZkoPD7qcQIvlg</t>
+  </si>
+  <si>
+    <t>UCx7m16BsXrMYxiroXh0_awQ</t>
+  </si>
+  <si>
+    <t>UCVSMxiK-0TSIOv1c3uRlZiQ</t>
+  </si>
+  <si>
+    <t>UCUFFSuNAD4PbSEpw_K5h0rA</t>
+  </si>
+  <si>
+    <t>UCOgPGtSnFR6GM-AkzCnxqMQ</t>
+  </si>
+  <si>
+    <t>UCNiXdX4GTsg2bd2nmGDLvNg</t>
+  </si>
+  <si>
+    <t>UCLtOrGKZ1t_qhHNG14RFZ0Q</t>
+  </si>
+  <si>
+    <t>UCrb8ENDcdCR54VTQVH6lIVA</t>
+  </si>
+  <si>
+    <t>UCLZgflun26j9V9n73zA2T5g</t>
+  </si>
+  <si>
+    <t>UCxI8LYakG709x4dlg0eybmA</t>
+  </si>
+  <si>
+    <t>UCycuPgtpxdu_6-1nVXgzPmg</t>
+  </si>
+  <si>
+    <t>UC2IEa6Iw_tfg_IiDnkDBVig</t>
+  </si>
+  <si>
+    <t>UCxTx5qfizauBQ-dofWliwhQ</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>UCQkU7oHk3P-qv_RBlo-l4yA</t>
+  </si>
+  <si>
+    <t>UCDw0K7K658-ztRuCn2mn0Kw</t>
+  </si>
+  <si>
+    <t>UCZt4nIjVCTcvVYzjp_VTJew</t>
+  </si>
+  <si>
+    <t>UCruX0f0QtZGDCZXMCp3Bn6A</t>
+  </si>
+  <si>
+    <t>UCwEJh0YIgmj-XfslMIf_7Kg</t>
+  </si>
+  <si>
+    <t>UCniL73VSz0Wkqsrq1px6OxA</t>
+  </si>
+  <si>
+    <t>UCbh5D3EdIHP4YQA5X-eK1ug</t>
+  </si>
+  <si>
+    <t>UCeKWO9gvmAyoPiEuaIwnGHQ</t>
+  </si>
+  <si>
+    <t>UCIJj1YP0E-EhdMI7a7BDgVQ</t>
+  </si>
+  <si>
+    <t>UCdEOBBKrRrUC1Sw4zWQyqcw</t>
+  </si>
+  <si>
+    <t>UCx7d4GbmiN5o8EPgSYW_mVw</t>
+  </si>
+  <si>
+    <t>UCBkfxC056lxHJ6QMUCKZHJw</t>
+  </si>
+  <si>
+    <t>UCayt-Tlv2B5ml563G8Uoo4w</t>
+  </si>
+  <si>
+    <t>UC5zKNgrnghGLAdUwT9SD7Dg</t>
+  </si>
+  <si>
+    <t>UCHnmeuSOn1Hscizw6otqWrA</t>
+  </si>
+  <si>
+    <t>UCzkV5QHCgkJ_2pbWBA2iVAA</t>
+  </si>
+  <si>
+    <t>UC0sfnuCUaYV2twmfZDtXZng</t>
+  </si>
+  <si>
+    <t>UCe5hl70Es-VQ4OWvxssFH4A</t>
+  </si>
+  <si>
+    <t>UCjSkyrjqPeMwubZU0CnScXA</t>
+  </si>
+  <si>
+    <t>UC2B5s_U1wu1R6d4M3Z5_hkQ</t>
+  </si>
+  <si>
+    <t>UCUtUTpAbCtIKOalhAK-hxZA</t>
+  </si>
+  <si>
+    <t>UCrroBKt5-4LAjMoB9LiNHzQ</t>
+  </si>
+  <si>
+    <t>UCg1gunjyxII91i4fkr-Sg8A</t>
+  </si>
+  <si>
+    <t>UC-5mMIF1gq5l6Nh5BuKX2qw</t>
+  </si>
+  <si>
+    <t>UCXKlu5bgL_gMgbVX2X2J-zg</t>
+  </si>
+  <si>
+    <t>UC4P0aWUxj39WrzVdbi1HPow</t>
+  </si>
+  <si>
+    <t>UCXUY7ZedAkeAH1jQBdoihKg</t>
+  </si>
+  <si>
+    <t>UCnKORmh-bQtifAT52hDi-pA</t>
+  </si>
+  <si>
+    <t>UCXpvI8jeu166he5e_Emo2ig</t>
+  </si>
+  <si>
+    <t>UCXTTZIvh1UAlf0kv6XHvOtg</t>
+  </si>
+  <si>
+    <t>UCLkHXX5R9S_qFZuCMGHWMrQ</t>
+  </si>
+  <si>
+    <t>UC1lSJPfMswLZcpyfzmkX5HA</t>
+  </si>
+  <si>
+    <t>UCxXmS6BkfhCALrPyCJKmPyg</t>
+  </si>
+  <si>
+    <t>UC_Ded3Gn7MCTzPg1LOZ7DxA</t>
+  </si>
+  <si>
+    <t>UCf4WJRXsgDEP7KH2eNGv8Hw</t>
+  </si>
+  <si>
+    <t>UCeVGpIFVLxTKU5dKMDOZfEA</t>
+  </si>
+  <si>
+    <t>UCF1ieyjAjqOePY-sXZp7hXg</t>
+  </si>
+  <si>
+    <t>UCgJ0yIYRJT13BPtQdagWORA</t>
+  </si>
+  <si>
+    <t>UCkcBTQj0kstb7cjYAr4k9AA</t>
+  </si>
+  <si>
+    <t>UClAphf8egdRMoPKgZRdv6fw</t>
+  </si>
+  <si>
+    <t>UC1hR9p3e6yzmjQcB7mRNF0g</t>
+  </si>
+  <si>
+    <t>UCixTpUBHGLlQb7qisAAzO9w</t>
+  </si>
+  <si>
+    <t>UCAe4VvNMKFlFnqT2fe9-0HA</t>
+  </si>
+  <si>
+    <t>UC1qFtRUgiodtHFWRs3RY1lg</t>
+  </si>
+  <si>
+    <t>UCT0Na5WfOReXDKUPwPtHYhw</t>
+  </si>
+  <si>
+    <t>UCDG7fluFPCLOmFz_Rhc3cXw</t>
+  </si>
+  <si>
+    <t>UCmsH6M-T0Sxn3aAnmZovkUg</t>
+  </si>
+  <si>
+    <t>UC4MU4vWHS8p7exa1AFd7F-g</t>
+  </si>
+  <si>
+    <t>UCi-pZ-VukgK9uzymsA0LNQA</t>
+  </si>
+  <si>
+    <t>UCLKkJCqSZVge1TfqfJpIikw</t>
+  </si>
+  <si>
+    <t>UCvfprbZVq18xQ3kX-Jo_yvg</t>
+  </si>
+  <si>
+    <t>UCP0XtrbAFWp-RkPS904VSEw</t>
+  </si>
+  <si>
+    <t>UCBwpPcCVc8EllWg2lWuVtlw</t>
+  </si>
+  <si>
+    <t>UCbLg0N7R6yzlvj-opejaCxw</t>
+  </si>
+  <si>
+    <t>UC-k-5F2j4CUzuwkx1QLRlpA</t>
   </si>
 </sst>
 </file>
@@ -1264,1307 +1592,2222 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B201"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.19921875" customWidth="1"/>
-    <col min="2" max="2" width="15.53125" customWidth="1"/>
+    <col min="1" max="1" width="28.21875" customWidth="1"/>
+    <col min="2" max="2" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B19" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B20" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B21" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B22" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B23" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B24" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>39</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>41</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>43</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B29" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>46</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>50</v>
       </c>
       <c r="B32" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>52</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B34" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B35" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>56</v>
       </c>
       <c r="B36" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B37" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>59</v>
       </c>
       <c r="B38" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>61</v>
       </c>
       <c r="B39" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>63</v>
       </c>
       <c r="B40" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B41" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>66</v>
       </c>
       <c r="B42" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>68</v>
       </c>
       <c r="B43" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B44" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>71</v>
       </c>
       <c r="B45" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>73</v>
       </c>
       <c r="B46" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
       </c>
       <c r="B47" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B48" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B49" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B50" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>80</v>
       </c>
       <c r="B51" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>82</v>
       </c>
       <c r="B52" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B53" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>85</v>
       </c>
       <c r="B54" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B55" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>88</v>
       </c>
       <c r="B56" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B57" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B58" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>92</v>
       </c>
       <c r="B59" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B60" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
       <c r="B61" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>97</v>
       </c>
       <c r="B62" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B63" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>100</v>
       </c>
       <c r="B64" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>102</v>
       </c>
       <c r="B65" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>104</v>
       </c>
       <c r="B66" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>106</v>
       </c>
       <c r="B67" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>108</v>
       </c>
       <c r="B68" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B69" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B70" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>112</v>
       </c>
       <c r="B71" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B72" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>115</v>
       </c>
       <c r="B73" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>117</v>
       </c>
       <c r="B74" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>119</v>
       </c>
       <c r="B75" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B76" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>122</v>
       </c>
       <c r="B77" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B78" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>125</v>
       </c>
       <c r="B79" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B80" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>128</v>
       </c>
       <c r="B81" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B82" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B83" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>132</v>
       </c>
       <c r="B84" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>134</v>
       </c>
       <c r="B85" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B86" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B87" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B88" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B89" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>140</v>
       </c>
       <c r="B90" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B91" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B92" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B93" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>145</v>
       </c>
       <c r="B94" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B95" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>148</v>
       </c>
       <c r="B96" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>150</v>
       </c>
       <c r="B97" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>152</v>
       </c>
       <c r="B98" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B99" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B100" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B101" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B102" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B103" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>159</v>
       </c>
       <c r="B104" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>161</v>
       </c>
       <c r="B105" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B106" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B107" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B108" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>166</v>
       </c>
       <c r="B109" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>168</v>
       </c>
       <c r="B110" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>170</v>
       </c>
       <c r="B111" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>172</v>
       </c>
       <c r="B112" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>174</v>
       </c>
       <c r="B113" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B114" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>177</v>
       </c>
       <c r="B115" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B116" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B117" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B118" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B119" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B120" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B121" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>185</v>
       </c>
       <c r="B122" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>187</v>
       </c>
       <c r="B123" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B124" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>190</v>
       </c>
       <c r="B125" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B126" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B127" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B128" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B129" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>196</v>
       </c>
       <c r="B130" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>198</v>
       </c>
       <c r="B131" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B132" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B133" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B134" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B135" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B136" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B137" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B138" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B139" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B140" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B141" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B142" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>211</v>
       </c>
       <c r="B143" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>213</v>
       </c>
       <c r="B144" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>215</v>
       </c>
       <c r="B145" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B146" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B147" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>219</v>
       </c>
       <c r="B148" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B149" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>222</v>
       </c>
       <c r="B150" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B151" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B152" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>226</v>
       </c>
       <c r="B153" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>228</v>
       </c>
       <c r="B154" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>230</v>
       </c>
       <c r="B155" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B156" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>233</v>
       </c>
       <c r="B157" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B158" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B159" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>237</v>
       </c>
       <c r="B160" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B161" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B162" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B163" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B164" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B165" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B166" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B167" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>246</v>
       </c>
       <c r="B168" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>248</v>
       </c>
       <c r="B169" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B170" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>251</v>
       </c>
       <c r="B171" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>253</v>
       </c>
       <c r="B172" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B173" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B174" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B175" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>258</v>
       </c>
       <c r="B176" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B177" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B178" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B179" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>263</v>
       </c>
       <c r="B180" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>265</v>
       </c>
       <c r="B181" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B182" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B183" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B184" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>270</v>
       </c>
       <c r="B185" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>272</v>
       </c>
       <c r="B186" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B187" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B188" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B189" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B190" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>278</v>
       </c>
       <c r="B191" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>280</v>
       </c>
       <c r="B192" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>282</v>
       </c>
       <c r="B193" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B194" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>285</v>
       </c>
       <c r="B195" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B196" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>288</v>
       </c>
       <c r="B197" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B198" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B199" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B200" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>293</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C201">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2573,6 +3816,110 @@
     <hyperlink ref="B11" r:id="rId2" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCfa7jJFYnn3P5LdJXsFkrjw" xr:uid="{E86851A7-8E35-43E1-A273-1BCE833AB2A9}"/>
     <hyperlink ref="B12" r:id="rId3" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC5E9-r42JlymhLPnDv2wHuA" xr:uid="{FBEF0938-12AA-44BF-B06C-6A8C7FF050F9}"/>
     <hyperlink ref="B15" r:id="rId4" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCh24_9600fCJemez4RgoOmw" xr:uid="{C9A76A93-DCC0-4D24-B155-7A70DAFB4E3F}"/>
+    <hyperlink ref="B19" r:id="rId5" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCb5TfGtSgvNPVPQawfCFuAw" xr:uid="{EEE051F3-0B8B-4C7D-A688-71524720D18A}"/>
+    <hyperlink ref="B20" r:id="rId6" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCBzai1GXVKDdVCrwlKZg_6Q" xr:uid="{77FA4BE2-55F0-4424-B0A4-0B41E71132C2}"/>
+    <hyperlink ref="B21" r:id="rId7" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCIk-Fw1QuWJdO4sAxhXE5DA" xr:uid="{CF098A58-6452-4FAE-AB40-8DF1F354D5BD}"/>
+    <hyperlink ref="B23" r:id="rId8" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UClCZul-nK9h8eVo7REC7RGA" xr:uid="{40D1DEEF-CB5F-48A4-B796-FAB31AF42139}"/>
+    <hyperlink ref="B24" r:id="rId9" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCYisdU_KhanzKLQlMPe5zGA" xr:uid="{998C4C72-9A74-4771-BFCD-CB6612275149}"/>
+    <hyperlink ref="B22" r:id="rId10" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCnVTsgPKj7tKrDAC2IsRp9A" xr:uid="{1CF34A5E-76E0-4924-8A80-D583BE0152A0}"/>
+    <hyperlink ref="B18" r:id="rId11" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCBnqM-sZxMRm2hnVo6wSQ8w" xr:uid="{7803D27F-FEFE-46DF-9167-125B221CA302}"/>
+    <hyperlink ref="B29" r:id="rId12" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCoKCF-pUbhJtSsSGs6JCLfQ" xr:uid="{28BF15B0-721B-4042-A51C-136B4E2D7FC7}"/>
+    <hyperlink ref="B34" r:id="rId13" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCCljzsYpepeNeY-nKPBKnhA" xr:uid="{926B0998-17D1-44DC-90CB-17791350EB6C}"/>
+    <hyperlink ref="B35" r:id="rId14" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCOQFfcGRc886dXP2Oyt5OEg" xr:uid="{E4FBBE8A-352A-4F25-A7EB-A6831495322B}"/>
+    <hyperlink ref="B37" r:id="rId15" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC4psZiwQ7Iw2ypKcK7k2a-A" xr:uid="{72210F23-7381-410E-A473-B2F9E8D5F206}"/>
+    <hyperlink ref="B41" r:id="rId16" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCOfQ0nZG7YClwNSaL-xULKQ" xr:uid="{67AB54AB-14DE-4A74-B97E-0E92B0B2DC3F}"/>
+    <hyperlink ref="B44" r:id="rId17" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCZPAni75bkLnjGO8yhuJpdw" xr:uid="{6A97ADDC-0678-4E24-A9A5-AEA36EB2B9A3}"/>
+    <hyperlink ref="B48" r:id="rId18" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCFn1ROV1cysLXMkS53Aw6PQ" xr:uid="{3623B8DC-2937-4A9B-BAFC-17A789E4CA04}"/>
+    <hyperlink ref="B49" r:id="rId19" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCiiGHI0DtajhSqQtf0478hA" xr:uid="{AEA86675-542B-4D29-B62E-3AC78AB7D944}"/>
+    <hyperlink ref="B50" r:id="rId20" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCgrHgV7atBftQk8dXwIDktg" xr:uid="{8490EED2-24DB-4340-B81B-C759CAC5A5EE}"/>
+    <hyperlink ref="B53" r:id="rId21" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCi7lrRpU8mVZ4QNCPIcadUw" xr:uid="{46B1FDF9-41A5-47C1-8BB1-ACB37F33719D}"/>
+    <hyperlink ref="B55" r:id="rId22" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC_d3KXxOJx2WaS4kQ5eJePw" xr:uid="{FCC03D32-9508-4AAB-9356-1542F634A5E9}"/>
+    <hyperlink ref="B57" r:id="rId23" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCnytvQ-VexQ43pYx6KX-DPw" xr:uid="{3CE30631-FA64-44F0-8B14-2F247A11D325}"/>
+    <hyperlink ref="B58" r:id="rId24" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCTkYT9IjUuhmkXbwYEohIwQ" xr:uid="{29E776CB-69AC-4D1A-9D8D-E03199F940BC}"/>
+    <hyperlink ref="B60" r:id="rId25" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC9Iq-yi4q3lsnSEXltzpqcQ" xr:uid="{F8F37F6C-51E7-4B48-999E-538266E2E57B}"/>
+    <hyperlink ref="B63" r:id="rId26" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCq880QL0THPePYuGKV7PxZw" xr:uid="{153B2899-0A7E-4AD8-9828-1C1B00D41E51}"/>
+    <hyperlink ref="B69" r:id="rId27" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCM5gP5bRLmc7ysiLbXA2R3A" xr:uid="{D9279EF9-4B9F-450D-908C-221B1EDD1EFA}"/>
+    <hyperlink ref="B70" r:id="rId28" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCIp8Syqe13rKfkybPq_udWQ" xr:uid="{07329527-653B-40D5-A93B-0A7217A9A8B6}"/>
+    <hyperlink ref="B72" r:id="rId29" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCBYxq7eD0UgOF0lGltd1ItQ" xr:uid="{25A5838D-B21E-4D39-9E12-1E5139301F29}"/>
+    <hyperlink ref="B76" r:id="rId30" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCeRAFi29YbP0de5LtRG2UMw" xr:uid="{647FFD1C-B541-4FE1-A9EE-9127D158627B}"/>
+    <hyperlink ref="B78" r:id="rId31" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCD52HZzU0qxNHUCEkPgSJaA" xr:uid="{B32539EE-9D92-4C6D-A753-0BE11234A180}"/>
+    <hyperlink ref="B80" r:id="rId32" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCqLv2nTsMB_FXtQRFNXjWhA" xr:uid="{0CAC9C71-501E-480B-AB6E-BA3A5E2F663E}"/>
+    <hyperlink ref="B82" r:id="rId33" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCGMVBv0w5tIGuwGT-Tgu2Lw" xr:uid="{01B0E0EC-67CE-4377-8616-6506359C1EF0}"/>
+    <hyperlink ref="B83" r:id="rId34" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCmW4T08z29y3VDAkPOIpIjg" xr:uid="{D61502CF-FB86-47EF-8DA6-725CD544073C}"/>
+    <hyperlink ref="B86" r:id="rId35" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCWZu-P34DVZUVrYAROU3Cmw" xr:uid="{B4434449-188C-44DE-BB85-13F0B63F82B8}"/>
+    <hyperlink ref="B87" r:id="rId36" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCfZhCLT9UmzRl1byZguPoHA" xr:uid="{F1E5CF03-FCFD-4B57-BCBB-B63DD0A031CC}"/>
+    <hyperlink ref="B88" r:id="rId37" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCxQTon4gUs00H48vEeFYmZQ" xr:uid="{2C01D722-D81C-4A0C-9C14-8F626405E6A7}"/>
+    <hyperlink ref="B89" r:id="rId38" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCa7IcQjnxZTOLgdNU14Hydg" xr:uid="{AC0DF508-B33D-406F-817F-2E55A4406E79}"/>
+    <hyperlink ref="B91" r:id="rId39" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UChiFVh8U2d6cyJIh0ghNF3w" xr:uid="{34D8A51F-BE36-4EB2-B792-A4E111134473}"/>
+    <hyperlink ref="B92" r:id="rId40" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCinuZeKpeDJRJ2w8n3PZmzg" xr:uid="{055E4B00-200C-42DC-906F-5117DD6B5676}"/>
+    <hyperlink ref="B93" r:id="rId41" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCJiRXf1Pb0ZkoPD7qcQIvlg" xr:uid="{D4581310-5D6C-4339-87A1-941CE64B90B4}"/>
+    <hyperlink ref="B95" r:id="rId42" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCx7m16BsXrMYxiroXh0_awQ" xr:uid="{3E767961-2759-404B-928A-7D4956C0679E}"/>
+    <hyperlink ref="B99" r:id="rId43" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCVSMxiK-0TSIOv1c3uRlZiQ" xr:uid="{E7E8DA9E-9A6B-4CED-89D3-F0EEEBA774AE}"/>
+    <hyperlink ref="B100" r:id="rId44" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCUFFSuNAD4PbSEpw_K5h0rA" xr:uid="{E7520945-5550-40FF-8992-179D70198724}"/>
+    <hyperlink ref="B101" r:id="rId45" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCOgPGtSnFR6GM-AkzCnxqMQ" xr:uid="{E570E2C5-74C9-4283-A2E8-49FFF8835281}"/>
+    <hyperlink ref="B102" r:id="rId46" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCNiXdX4GTsg2bd2nmGDLvNg" xr:uid="{7D484610-642F-49A6-9A99-B2280AA702A4}"/>
+    <hyperlink ref="B103" r:id="rId47" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCLtOrGKZ1t_qhHNG14RFZ0Q" xr:uid="{A3CD4BAC-A24B-472D-9BCB-46F5984445C7}"/>
+    <hyperlink ref="B106" r:id="rId48" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCrb8ENDcdCR54VTQVH6lIVA" xr:uid="{40A4CBA3-7FA5-42AF-8619-875872F8F1BC}"/>
+    <hyperlink ref="B107" r:id="rId49" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCLZgflun26j9V9n73zA2T5g" xr:uid="{78F9182D-3746-4D3A-B2FB-78401B42939B}"/>
+    <hyperlink ref="B108" r:id="rId50" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCxI8LYakG709x4dlg0eybmA" xr:uid="{F67124F6-7F58-49E1-9E0B-CFDF35029C30}"/>
+    <hyperlink ref="B114" r:id="rId51" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCycuPgtpxdu_6-1nVXgzPmg" xr:uid="{B340B564-7C45-4A76-A052-796408FA3538}"/>
+    <hyperlink ref="B116" r:id="rId52" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC2IEa6Iw_tfg_IiDnkDBVig" xr:uid="{4290C807-10C9-47AB-8BD4-410EFC83397B}"/>
+    <hyperlink ref="B117" r:id="rId53" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCxTx5qfizauBQ-dofWliwhQ" xr:uid="{C2339689-D6A5-45C7-8AB4-1072D44B2B86}"/>
+    <hyperlink ref="B118" r:id="rId54" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCQkU7oHk3P-qv_RBlo-l4yA" xr:uid="{C2F72959-C583-48B4-A365-5ADD4AC5B8B1}"/>
+    <hyperlink ref="B119" r:id="rId55" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCDw0K7K658-ztRuCn2mn0Kw" xr:uid="{3BDCD14B-17BD-4E21-8C27-7D07A779F00A}"/>
+    <hyperlink ref="B120" r:id="rId56" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCZt4nIjVCTcvVYzjp_VTJew" xr:uid="{A4FD0E7F-FBC8-4D16-AFCF-7F64C032BBBE}"/>
+    <hyperlink ref="B121" r:id="rId57" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCruX0f0QtZGDCZXMCp3Bn6A" xr:uid="{49FE5CEB-8D34-4CD4-BE53-4588868F363A}"/>
+    <hyperlink ref="B124" r:id="rId58" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCwEJh0YIgmj-XfslMIf_7Kg" xr:uid="{052295D4-6A53-4DAE-B23E-3AA122A37B9B}"/>
+    <hyperlink ref="B126" r:id="rId59" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCniL73VSz0Wkqsrq1px6OxA" xr:uid="{E57792C6-4731-44CE-B5FF-799AB0D6EAFB}"/>
+    <hyperlink ref="B127" r:id="rId60" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCbh5D3EdIHP4YQA5X-eK1ug" xr:uid="{F9C55E0C-6C80-4B24-9F89-4141918EE17C}"/>
+    <hyperlink ref="B128" r:id="rId61" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCeKWO9gvmAyoPiEuaIwnGHQ" xr:uid="{0365A351-330B-4BDC-B34A-11A546880340}"/>
+    <hyperlink ref="B129" r:id="rId62" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCIJj1YP0E-EhdMI7a7BDgVQ" xr:uid="{CB0954DB-5C86-4C1B-B31C-0269DAB23143}"/>
+    <hyperlink ref="B132" r:id="rId63" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCdEOBBKrRrUC1Sw4zWQyqcw" xr:uid="{A5876C19-4712-4A26-B219-6F798DD2D837}"/>
+    <hyperlink ref="B133" r:id="rId64" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCx7d4GbmiN5o8EPgSYW_mVw" xr:uid="{B10F3A8D-0C00-4A28-B2DA-BE6A7B0FA2B5}"/>
+    <hyperlink ref="B134" r:id="rId65" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCBkfxC056lxHJ6QMUCKZHJw" xr:uid="{3BF4139A-F6E4-405E-BA7E-2DAA4CB035C8}"/>
+    <hyperlink ref="B135" r:id="rId66" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCayt-Tlv2B5ml563G8Uoo4w" xr:uid="{AB88298B-2F11-4749-BBA6-04EC3042C895}"/>
+    <hyperlink ref="B136" r:id="rId67" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC5zKNgrnghGLAdUwT9SD7Dg" xr:uid="{4F9D6696-A3F8-4EE8-A869-D37D5E923F64}"/>
+    <hyperlink ref="B137" r:id="rId68" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCHnmeuSOn1Hscizw6otqWrA" xr:uid="{9FF6AB14-7273-43B6-A846-AEFF48840C05}"/>
+    <hyperlink ref="B138" r:id="rId69" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCzkV5QHCgkJ_2pbWBA2iVAA" xr:uid="{A3F57984-D8E7-4E01-B6EE-4C090EF98F6E}"/>
+    <hyperlink ref="B139" r:id="rId70" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC0sfnuCUaYV2twmfZDtXZng" xr:uid="{15F18029-0C7E-447C-9804-2625FB93ED87}"/>
+    <hyperlink ref="B140" r:id="rId71" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCe5hl70Es-VQ4OWvxssFH4A" xr:uid="{1A5F630B-0CA9-4796-8660-6E8864833B4B}"/>
+    <hyperlink ref="B141" r:id="rId72" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCjSkyrjqPeMwubZU0CnScXA" xr:uid="{6D11B871-2BC2-417F-9B9F-8F72C631E035}"/>
+    <hyperlink ref="B142" r:id="rId73" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC2B5s_U1wu1R6d4M3Z5_hkQ" xr:uid="{C469DD7B-21C6-4128-814F-097E7580F266}"/>
+    <hyperlink ref="B146" r:id="rId74" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCUtUTpAbCtIKOalhAK-hxZA" xr:uid="{32B5D66C-7F72-43E5-840E-B310B9BDBE7E}"/>
+    <hyperlink ref="B147" r:id="rId75" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCrroBKt5-4LAjMoB9LiNHzQ" xr:uid="{E4B6C48F-0CD6-480A-AF52-971A6E1B511B}"/>
+    <hyperlink ref="B149" r:id="rId76" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCg1gunjyxII91i4fkr-Sg8A" xr:uid="{699144D1-E77D-4E44-8A2A-92558B6FE400}"/>
+    <hyperlink ref="B151" r:id="rId77" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC-5mMIF1gq5l6Nh5BuKX2qw" xr:uid="{633DA079-D8DF-486D-90B5-A189BFFA2B7D}"/>
+    <hyperlink ref="B152" r:id="rId78" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCXKlu5bgL_gMgbVX2X2J-zg" xr:uid="{951CBFA9-4EC7-4CD9-89A3-DC06F60FE57D}"/>
+    <hyperlink ref="B156" r:id="rId79" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC4P0aWUxj39WrzVdbi1HPow" xr:uid="{AC94F7FE-7BC9-4EB9-BADD-40F43281465A}"/>
+    <hyperlink ref="B158" r:id="rId80" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCXUY7ZedAkeAH1jQBdoihKg" xr:uid="{7211B42C-53B0-49E2-844D-4602464D0D3C}"/>
+    <hyperlink ref="B159" r:id="rId81" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCnKORmh-bQtifAT52hDi-pA" xr:uid="{16AB9FC5-6B39-4EF0-AF8B-DEEB1FE33516}"/>
+    <hyperlink ref="B161" r:id="rId82" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCXpvI8jeu166he5e_Emo2ig" xr:uid="{FF8D2D96-0AAF-4E2D-ABB7-864C9DE8CE93}"/>
+    <hyperlink ref="B162" r:id="rId83" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCXTTZIvh1UAlf0kv6XHvOtg" xr:uid="{9E3E80D4-3091-4D7E-A416-3192DAD5B7CB}"/>
+    <hyperlink ref="B163" r:id="rId84" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCLkHXX5R9S_qFZuCMGHWMrQ" xr:uid="{5FF897AB-8B92-4924-AA74-30503F4CD391}"/>
+    <hyperlink ref="B165" r:id="rId85" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC1lSJPfMswLZcpyfzmkX5HA" xr:uid="{7F81CA63-E6A5-41E6-9394-776F584F1FD5}"/>
+    <hyperlink ref="B164" r:id="rId86" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCxXmS6BkfhCALrPyCJKmPyg" xr:uid="{D96E0AC0-DE8E-4AD9-83A9-4553695C994B}"/>
+    <hyperlink ref="B166" r:id="rId87" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC_Ded3Gn7MCTzPg1LOZ7DxA" xr:uid="{993591EF-9F6E-41AD-BECE-9FBAC2A13E7A}"/>
+    <hyperlink ref="B167" r:id="rId88" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCf4WJRXsgDEP7KH2eNGv8Hw" xr:uid="{5216B776-85F9-4DF7-B93D-50219AA7E67A}"/>
+    <hyperlink ref="B170" r:id="rId89" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCeVGpIFVLxTKU5dKMDOZfEA" xr:uid="{5380DA49-96B6-41DC-B59D-800D382E62D0}"/>
+    <hyperlink ref="B173" r:id="rId90" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCF1ieyjAjqOePY-sXZp7hXg" xr:uid="{CEDE5DD3-05A7-409C-B7AD-B645059451E7}"/>
+    <hyperlink ref="B174" r:id="rId91" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCgJ0yIYRJT13BPtQdagWORA" xr:uid="{903AEE48-31C8-499D-B46E-3371AE09297E}"/>
+    <hyperlink ref="B175" r:id="rId92" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCkcBTQj0kstb7cjYAr4k9AA" xr:uid="{0D05289C-4568-4661-B99A-961986FD481E}"/>
+    <hyperlink ref="B177" r:id="rId93" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UClAphf8egdRMoPKgZRdv6fw" xr:uid="{EE69218C-E4D3-4337-BF6B-A93519DE7B8C}"/>
+    <hyperlink ref="B178" r:id="rId94" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC1hR9p3e6yzmjQcB7mRNF0g" xr:uid="{F7595E93-998B-4069-ACE7-07C07D92CC16}"/>
+    <hyperlink ref="B179" r:id="rId95" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCixTpUBHGLlQb7qisAAzO9w" xr:uid="{4CEA920B-651B-4BD0-88A7-5B5B9F545B57}"/>
+    <hyperlink ref="B182" r:id="rId96" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCAe4VvNMKFlFnqT2fe9-0HA" xr:uid="{624BC9A7-83F2-41C1-B42B-00EC4459AC32}"/>
+    <hyperlink ref="B183" r:id="rId97" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC1qFtRUgiodtHFWRs3RY1lg" xr:uid="{234C7830-1642-440E-8EC3-122808FCB4D4}"/>
+    <hyperlink ref="B184" r:id="rId98" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCT0Na5WfOReXDKUPwPtHYhw" xr:uid="{A1386829-8E15-4329-AF56-F1B1B564FF63}"/>
+    <hyperlink ref="B187" r:id="rId99" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCDG7fluFPCLOmFz_Rhc3cXw" xr:uid="{300D2E11-6811-46C8-AE84-9AD162B4B633}"/>
+    <hyperlink ref="B188" r:id="rId100" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCmsH6M-T0Sxn3aAnmZovkUg" xr:uid="{81192B21-CCF1-4BA2-B396-63C54F7BDBF4}"/>
+    <hyperlink ref="B189" r:id="rId101" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC4MU4vWHS8p7exa1AFd7F-g" xr:uid="{BBE76F26-73D5-4DFD-94B2-0A4B4FE87D93}"/>
+    <hyperlink ref="B190" r:id="rId102" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCi-pZ-VukgK9uzymsA0LNQA" xr:uid="{125126C0-4F6E-47BC-8DBB-B7A68883B37C}"/>
+    <hyperlink ref="B194" r:id="rId103" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCLKkJCqSZVge1TfqfJpIikw" xr:uid="{070B4774-FFC4-4863-8963-3124B606C99C}"/>
+    <hyperlink ref="B196" r:id="rId104" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCvfprbZVq18xQ3kX-Jo_yvg" xr:uid="{DD45E461-6522-485F-A30B-63C3916E3653}"/>
+    <hyperlink ref="B198" r:id="rId105" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCP0XtrbAFWp-RkPS904VSEw" xr:uid="{C81DE29B-9C63-493B-A740-89E9DCB22B96}"/>
+    <hyperlink ref="B199" r:id="rId106" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCBwpPcCVc8EllWg2lWuVtlw" xr:uid="{9B13AC31-6937-4EC2-82CF-F39D3F9216D9}"/>
+    <hyperlink ref="B200" r:id="rId107" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UCbLg0N7R6yzlvj-opejaCxw" xr:uid="{61A5E5FA-2FD8-4384-974F-3CBDDDDE75F1}"/>
+    <hyperlink ref="B201" r:id="rId108" display="view-source:https://www.youtube.com/feeds/videos.xml?channel_id=UC-k-5F2j4CUzuwkx1QLRlpA" xr:uid="{763A7A2C-CBE8-4F37-89F8-FE85ACDC8B32}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
